--- a/pages/Time_Trial_Points_Women.xlsx
+++ b/pages/Time_Trial_Points_Women.xlsx
@@ -13171,22 +13171,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>VASQUEZ AVILA Elizabeth</t>
+          <t>SOLOVYEVA Anzhela</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>10010086263</t>
+          <t>10036104087</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>12 Apr 2023</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CAMPEONATO NACIONAL DE PISTA 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Kazakhstan National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -13223,22 +13223,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SOLOVYEVA Anzhela</t>
+          <t>GENEST Lauriane (NCI)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>10036104087</t>
+          <t>10011157206</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>12 Apr 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kazakhstan National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -13275,22 +13275,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>GENEST Lauriane (NCI)</t>
+          <t>SAKAI Aki</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>10011157206</t>
+          <t>10021474972</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>12 May 2023</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
+          <t>Japan Track National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">

--- a/pages/Time_Trial_Points_Women.xlsx
+++ b/pages/Time_Trial_Points_Women.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J248"/>
+  <dimension ref="A1:J250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04 Sep 2022</t>
+          <t>09 Jun 2023</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Campeonatos de Espana de Pista Open (Elite-Sub23) - Women Elite - Time Trial - General Classification</t>
+          <t>CAMPEONATO ESPAÑA PISTA OPEN Y CICLISMO ADAPTADO - GP HYUNDAI MARCOS AUTOMOCION - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6255,47 +6255,47 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KARWACKA Marlena</t>
+          <t>BILETSKA Alla</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10010098589</t>
+          <t>10075826193</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>474.00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6307,22 +6307,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KARWACKA Marlena</t>
+          <t>BILETSKA Alla</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>10010098589</t>
+          <t>10075826193</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>01 Jun 2023</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6332,22 +6332,22 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship of Ukraine - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>474.00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6359,146 +6359,146 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AYUBA Grace</t>
+          <t>BILETSKA Alla</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10076778716</t>
+          <t>10075826193</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NGR</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>474.00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KAKHKHOROVA Madina (TTT)</t>
+          <t>BILETSKA Alla</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10093733306</t>
+          <t>10075826193</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>22 Jun 2022</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Elite and Junior Asian Track Cycling Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>474.00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KAKHKHOROVA Madina (TTT)</t>
+          <t>KARWACKA Marlena</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10093733306</t>
+          <t>10010098589</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20 Aug 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>The National Championship of Uzbekistan - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6508,81 +6508,81 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RECIO CARVAJAL Abigail</t>
+          <t>KARWACKA Marlena</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10016297293</t>
+          <t>10010098589</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>436.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RECIO CARVAJAL Abigail</t>
+          <t>AYUBA Grace</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10016297293</t>
+          <t>10076778716</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>NGR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6592,74 +6592,74 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>450</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>436.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RECIO CARVAJAL Abigail</t>
+          <t>KAKHKHOROVA Madina (TTT)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>10016297293</t>
+          <t>10093733306</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>22 Jun 2022</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
+          <t>Elite and Junior Asian Track Cycling Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>436.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6671,344 +6671,344 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VAN NIEKERK Danielle</t>
+          <t>KAKHKHOROVA Madina (TTT)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>10010823261</t>
+          <t>10093733306</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>20 Aug 2022</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
+          <t>The National Championship of Uzbekistan - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MARCHANT Katy (TIN)</t>
+          <t>RECIO CARVAJAL Abigail</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10009195883</t>
+          <t>10016297293</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>436.00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MARCHANT Katy (TIN)</t>
+          <t>RECIO CARVAJAL Abigail</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10009195883</t>
+          <t>10016297293</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>436.00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CLARK Tomasin</t>
+          <t>RECIO CARVAJAL Abigail</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10140426678</t>
+          <t>10016297293</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>415.00</t>
+          <t>436.00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CLARK Tomasin</t>
+          <t>VAN NIEKERK Danielle</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>10140426678</t>
+          <t>10010823261</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>420</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>415.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LOS Urszula</t>
+          <t>MARCHANT Katy (TIN)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>10007793326</t>
+          <t>10009195883</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LOS Urszula</t>
+          <t>MARCHANT Katy (TIN)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>10007793326</t>
+          <t>10009195883</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7023,24 +7023,24 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WATTS Sophie</t>
+          <t>CLARK Tomasin</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>10128740808</t>
+          <t>10140426678</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7065,34 +7065,34 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>405.00</t>
+          <t>415.00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>WATTS Sophie</t>
+          <t>CLARK Tomasin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>10128740808</t>
+          <t>10140426678</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7117,96 +7117,96 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>405.00</t>
+          <t>415.00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>YEUNG Cho Yiu</t>
+          <t>LOS Urszula</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10045965957</t>
+          <t>10007793326</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>320</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>404.00</t>
+          <t>410.00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>YEUNG Cho Yiu</t>
+          <t>LOS Urszula</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>10045965957</t>
+          <t>10007793326</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7216,74 +7216,74 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hong Kong National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>404.00</t>
+          <t>410.00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>YEUNG Cho Yiu</t>
+          <t>LOHVINIUK Oleksandra</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>10045965957</t>
+          <t>10034884921</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>404.00</t>
+          <t>406.00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7295,126 +7295,126 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KOUAME Affoué Sarah</t>
+          <t>LOHVINIUK Oleksandra</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>10062578118</t>
+          <t>10034884921</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>01 Jun 2023</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship of Ukraine - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>390.00</t>
+          <t>406.00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HADAVAND Fatemeh</t>
+          <t>LOHVINIUK Oleksandra</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>10131418008</t>
+          <t>10034884921</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IRI</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>22 Jun 2022</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Elite and Junior Asian Track Cycling Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>390.00</t>
+          <t>406.00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BILETSKA Alla</t>
+          <t>WATTS Sophie</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>10075826193</t>
+          <t>10128740808</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7424,205 +7424,205 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>405.00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BILETSKA Alla</t>
+          <t>WATTS Sophie</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>10075826193</t>
+          <t>10128740808</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>405.00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BILETSKA Alla</t>
+          <t>YEUNG Cho Yiu</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>10075826193</t>
+          <t>10045965957</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>304</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ROBINSON Kalinda</t>
+          <t>YEUNG Cho Yiu</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>10097392125</t>
+          <t>10045965957</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Hong Kong National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>370.00</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ROBINSON Kalinda</t>
+          <t>YEUNG Cho Yiu</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>10097392125</t>
+          <t>10045965957</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7632,44 +7632,44 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>370.00</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>METOEVI Charlotte</t>
+          <t>KOUAME Affoué Sarah</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>10131438923</t>
+          <t>10062578118</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7689,44 +7689,44 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>360.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PETRI Paulina</t>
+          <t>HADAVAND Fatemeh</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>10053771225</t>
+          <t>10131418008</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>IRI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>22 Jun 2022</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7736,153 +7736,153 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Elite and Junior Asian Track Cycling Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PETRI Paulina</t>
+          <t>ROBINSON Kalinda</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>10053771225</t>
+          <t>10097392125</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>370.00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EMMANUELLA Rukundo</t>
+          <t>ROBINSON Kalinda</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>10127764239</t>
+          <t>10097392125</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>330.00</t>
+          <t>370.00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GUERRA RODRIGUEZ Lisandra</t>
+          <t>METOEVI Charlotte</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>10004594750</t>
+          <t>10131438923</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7892,49 +7892,49 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>330.00</t>
+          <t>360.00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HO Selina</t>
+          <t>PETRI Paulina</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>10015578382</t>
+          <t>10053771225</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -7959,34 +7959,34 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>330.00</t>
+          <t>345.00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HO Selina</t>
+          <t>PETRI Paulina</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>10015578382</t>
+          <t>10053771225</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7996,49 +7996,49 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>330.00</t>
+          <t>345.00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>LENDEL Migle</t>
+          <t>EMMANUELLA Rukundo</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>10133175627</t>
+          <t>10127764239</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8048,101 +8048,101 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>CAC Track African Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>330.00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LENDEL Migle</t>
+          <t>GUERRA RODRIGUEZ Lisandra</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>10133175627</t>
+          <t>10004594750</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>330.00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COLILEF BARRIOS Daniela</t>
+          <t>HO Selina</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>10053568131</t>
+          <t>10015578382</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8152,49 +8152,49 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>330.00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COLILEF BARRIOS Daniela</t>
+          <t>HO Selina</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>10053568131</t>
+          <t>10015578382</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>11 Dec 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8204,44 +8204,44 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Campeonato Nacional Pista de Chile - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>330.00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SIBIAK Nikola</t>
+          <t>LENDEL Migle</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>10016111983</t>
+          <t>10133175627</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8261,96 +8261,96 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SIBIAK Nikola</t>
+          <t>LENDEL Migle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>10016111983</t>
+          <t>10133175627</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JENAER Valerie</t>
+          <t>COLILEF BARRIOS Daniela</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>10110977983</t>
+          <t>10053568131</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8360,49 +8360,49 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JENAER Valerie</t>
+          <t>COLILEF BARRIOS Daniela</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>10110977983</t>
+          <t>10053568131</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>11 Dec 2022</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Nacional Pista de Chile - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8427,29 +8427,29 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LOHVINIUK Oleksandra</t>
+          <t>SIBIAK Nikola</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>10034884921</t>
+          <t>10016111983</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8469,96 +8469,96 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>246</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>306.00</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LOHVINIUK Oleksandra</t>
+          <t>SIBIAK Nikola</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>10034884921</t>
+          <t>10016111983</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>306.00</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AINSLIE Keely</t>
+          <t>JENAER Valerie</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>10007476963</t>
+          <t>10110977983</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8568,111 +8568,111 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>310.00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BENNETT Eliza</t>
+          <t>JENAER Valerie</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>10083950450</t>
+          <t>10110977983</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>23 Dec 2022</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>296.00</t>
+          <t>310.00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BENNETT Eliza</t>
+          <t>AINSLIE Keely</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>10083950450</t>
+          <t>10007476963</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -8682,39 +8682,39 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>296.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MARTINEZ GONZALEZ Carliany</t>
+          <t>BENNETT Eliza</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>10095256004</t>
+          <t>10083950450</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8724,49 +8724,49 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>246</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>292.00</t>
+          <t>296.00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MARTINEZ GONZALEZ Carliany</t>
+          <t>BENNETT Eliza</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>10095256004</t>
+          <t>10083950450</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>01 Oct 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8776,49 +8776,49 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Venezuela Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>292.00</t>
+          <t>296.00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CAPOBIANCHI Giada</t>
+          <t>MARTINEZ GONZALEZ Carliany</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>10029804040</t>
+          <t>10095256004</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8828,49 +8828,49 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>283.00</t>
+          <t>292.00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CAPOBIANCHI Giada</t>
+          <t>MARTINEZ GONZALEZ Carliany</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>10029804040</t>
+          <t>10095256004</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>22 Sep 2022</t>
+          <t>01 Oct 2022</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8880,27 +8880,27 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CAMPIONATO ITALIANO PISTA ELITE - Women Elite - Time Trial - General Classification</t>
+          <t>Venezuela Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>283.00</t>
+          <t>292.00</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -8922,27 +8922,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8959,89 +8959,89 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DALGER Tachana</t>
+          <t>CAPOBIANCHI Giada</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>10016292748</t>
+          <t>10029804040</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>22 Sep 2022</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>CAMPIONATO ITALIANO PISTA ELITE - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>274.00</t>
+          <t>283.00</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DALGER Tachana</t>
+          <t>CAPOBIANCHI Giada</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>10016292748</t>
+          <t>10029804040</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>13 Nov 2022</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9051,34 +9051,34 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>274.00</t>
+          <t>283.00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SYKES Amelia</t>
+          <t>DALGER Tachana</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>10075682010</t>
+          <t>10016292748</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -9108,39 +9108,39 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SYKES Amelia</t>
+          <t>DALGER Tachana</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>10075682010</t>
+          <t>10016292748</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>05 Mar 2023</t>
+          <t>13 Nov 2022</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Track National Championships 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -9160,24 +9160,24 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BLINCO Deneaka</t>
+          <t>SYKES Amelia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>10096589146</t>
+          <t>10075682010</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9197,44 +9197,44 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>274.00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BLINCO Deneaka</t>
+          <t>SYKES Amelia</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>10096589146</t>
+          <t>10075682010</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>05 Mar 2023</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9244,101 +9244,101 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Track National Championships 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>274.00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ROSIDI Anis Amira</t>
+          <t>BLINCO Deneaka</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>10010798003</t>
+          <t>10096589146</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>265.00</t>
+          <t>273.00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ROSIDI Anis Amira</t>
+          <t>BLINCO Deneaka</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>10010798003</t>
+          <t>10096589146</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9348,27 +9348,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KEJOHANAN TREK KEBANGSAAN 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>265.00</t>
+          <t>273.00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>117</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9452,17 +9452,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>KEJOHANAN TREK KEBANGSAAN 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9479,74 +9479,74 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NG Sze Wing (HKS)</t>
+          <t>ROSIDI Anis Amira</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>10045965149</t>
+          <t>10010798003</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>256.00</t>
+          <t>265.00</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NG Sze Wing (HKS)</t>
+          <t>ROSIDI Anis Amira</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>10045965149</t>
+          <t>10010798003</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9556,101 +9556,101 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hong Kong National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>256.00</t>
+          <t>265.00</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NOCK Jacqueline</t>
+          <t>NG Sze Wing (HKS)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>10136962364</t>
+          <t>10045965149</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>251.00</t>
+          <t>256.00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NOCK Jacqueline</t>
+          <t>NG Sze Wing (HKS)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>10136962364</t>
+          <t>10045965149</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9660,309 +9660,309 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Hong Kong National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>251.00</t>
+          <t>256.00</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CAPEWELL Sophie (TIN)</t>
+          <t>NOCK Jacqueline</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>10010171442</t>
+          <t>10136962364</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>29 Jan 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>250.00</t>
+          <t>251.00</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CAPEWELL Sophie (TIN)</t>
+          <t>NOCK Jacqueline</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>10010171442</t>
+          <t>10136962364</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>250.00</t>
+          <t>251.00</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VIZCAINO GARCIA Maria</t>
+          <t>CAPEWELL Sophie (TIN)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>10096093941</t>
+          <t>10010171442</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>246.00</t>
+          <t>250.00</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MOLINA RODRIGUEZ Paula</t>
+          <t>CAPEWELL Sophie (TIN)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10056608978</t>
+          <t>10010171442</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>236.00</t>
+          <t>250.00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MOLINA RODRIGUEZ Paula</t>
+          <t>VIZCAINO GARCIA Maria</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>10056608978</t>
+          <t>10096093941</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>11 Dec 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Campeonato Nacional Pista de Chile - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>246</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>236.00</t>
+          <t>246.00</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LYSAGHT Indiana</t>
+          <t>MOLINA RODRIGUEZ Paula</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>10128713021</t>
+          <t>10056608978</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9972,49 +9972,49 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>230.00</t>
+          <t>236.00</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LYSAGHT Indiana</t>
+          <t>MOLINA RODRIGUEZ Paula</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>10128713021</t>
+          <t>10056608978</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>11 Dec 2022</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10024,131 +10024,131 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Nacional Pista de Chile - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>230.00</t>
+          <t>236.00</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RIDGE-DAVIS Blaine (TIN)</t>
+          <t>LYSAGHT Indiana</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>10011100420</t>
+          <t>10128713021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>29 Jan 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>230.00</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RIDGE-DAVIS Blaine (TIN)</t>
+          <t>LYSAGHT Indiana</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>10011100420</t>
+          <t>10128713021</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>230.00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -10170,27 +10170,27 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
+          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10207,146 +10207,146 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DIAZ GUERRA Thalia</t>
+          <t>RIDGE-DAVIS Blaine (TIN)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>10093661766</t>
+          <t>10011100420</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>212.00</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NICOLAES Julie</t>
+          <t>RIDGE-DAVIS Blaine (TIN)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>10065045049</t>
+          <t>10011100420</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>212.00</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NICOLAES Julie</t>
+          <t>DIAZ GUERRA Thalia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>10065045049</t>
+          <t>10093661766</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10356,29 +10356,29 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RODRIGUEZ MARTINES Jalymar Elianna</t>
+          <t>NICOLAES Julie</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10095257721</t>
+          <t>10065045049</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -10408,29 +10408,29 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RODRIGUEZ MARTINES Jalymar Elianna</t>
+          <t>NICOLAES Julie</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>10095257721</t>
+          <t>10065045049</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>01 Oct 2022</t>
+          <t>23 Dec 2022</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Venezuela Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -10460,289 +10460,289 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RAMIREZ NORIEGA Melanie Janet</t>
+          <t>RODRIGUEZ MARTINES Jalymar Elianna</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>10016294465</t>
+          <t>10095257721</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>208.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STEVENS Emma</t>
+          <t>RODRIGUEZ MARTINES Jalymar Elianna</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>10115010961</t>
+          <t>10095257721</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>01 Oct 2022</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Venezuela Campeonato Nacional de Pista - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>191.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STEVENS Emma</t>
+          <t>RAMIREZ NORIEGA Melanie Janet</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>10115010961</t>
+          <t>10016294465</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>191.00</t>
+          <t>208.00</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KALEE Kimberly</t>
+          <t>STEVENS Emma</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>10064453955</t>
+          <t>10115010961</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NC Duur-Sprint - Women Elite - Time Trial - General Classification</t>
+          <t>2023 Oceania Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>191.00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>KALEE Kimberly</t>
+          <t>STEVENS Emma</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>10064453955</t>
+          <t>10115010961</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>191.00</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PALMER Dahlia</t>
+          <t>KALEE Kimberly</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10045952924</t>
+          <t>10064453955</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>11 Sep 2022</t>
+          <t>27 Dec 2022</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Jamaica National Track Championship - Women Elite - Time Trial - General Classification</t>
+          <t>NC Duur-Sprint - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -10772,44 +10772,44 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PALMER Dahlia</t>
+          <t>KALEE Kimberly</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>10045952924</t>
+          <t>10064453955</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>13 Nov 2022</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10824,29 +10824,29 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SPERLICH Christina</t>
+          <t>PALMER Dahlia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>10036438840</t>
+          <t>10045952924</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>11 Sep 2022</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10856,101 +10856,101 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>German National Championships Track 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>Jamaica National Track Championship - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>190.00</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SPERLICH Christina</t>
+          <t>PALMER Dahlia</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10036438840</t>
+          <t>10045952924</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>13 Nov 2022</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>190.00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SAMOKIŠINA Karina</t>
+          <t>SPERLICH Christina</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>10080711761</t>
+          <t>10036438840</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>02 Oct 2022</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10960,17 +10960,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lithuanian National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>German National Championships Track 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10980,49 +10980,49 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SAMOKIŠINA Karina</t>
+          <t>SPERLICH Christina</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>10080711761</t>
+          <t>10036438840</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11032,29 +11032,29 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SEYJAGAT Adrianna</t>
+          <t>SAMOKIŠINA Karina</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>10045939382</t>
+          <t>10080711761</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>02 Oct 2022</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>National Track Championships - Elite - Women Elite - Time Trial - General Classification</t>
+          <t>Lithuanian National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11084,29 +11084,29 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SEYJAGAT Adrianna</t>
+          <t>SAMOKIŠINA Karina</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>10045939382</t>
+          <t>10080711761</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>13 Nov 2022</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11136,29 +11136,29 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GERAERTS Lonneke</t>
+          <t>SEYJAGAT Adrianna</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>10023297158</t>
+          <t>10045939382</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>04 May 2023</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11168,183 +11168,183 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>NC Duur-Sprint - Women Elite - Time Trial - General Classification</t>
+          <t>National Track Championships - Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>166.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GERAERTS Lonneke</t>
+          <t>SEYJAGAT Adrianna</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>10023297158</t>
+          <t>10045939382</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>13 Nov 2022</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Caribbean Track Championships 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>166.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AZIZAN Nurul Aliana Syafika</t>
+          <t>GERAERTS Lonneke</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>10056177128</t>
+          <t>10023297158</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>27 Dec 2022</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
+          <t>NC Duur-Sprint - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>166.00</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AZIZAN Nurul Aliana Syafika</t>
+          <t>GERAERTS Lonneke</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>10056177128</t>
+          <t>10023297158</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>KEJOHANAN TREK KEBANGSAAN 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>166.00</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -11366,27 +11366,27 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track World Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -11403,74 +11403,74 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PATERNOSTER Letizia</t>
+          <t>AZIZAN Nurul Aliana Syafika</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>10015336387</t>
+          <t>10056177128</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
+          <t>KEJOHANAN TREK KEBANGSAAN 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TANNER Millicent (TIN)</t>
+          <t>AZIZAN Nurul Aliana Syafika</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>10064452844</t>
+          <t>10056177128</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>29 Jan 2023</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -11495,54 +11495,54 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TANNER Millicent (TIN)</t>
+          <t>PATERNOSTER Letizia</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>10064452844</t>
+          <t>10015336387</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -11552,29 +11552,29 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WOLFS Zoë</t>
+          <t>TANNER Millicent (TIN)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>10065055052</t>
+          <t>10064452844</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11584,101 +11584,101 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
+          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>155.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>WOLFS Zoë</t>
+          <t>TANNER Millicent (TIN)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>10065055052</t>
+          <t>10064452844</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>155.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BLASZCZAK Joanna</t>
+          <t>WOLFS Zoë</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>10052493754</t>
+          <t>10065055052</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>23 Dec 2022</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11688,101 +11688,101 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship - Track - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>155.00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BLASZCZAK Joanna</t>
+          <t>WOLFS Zoë</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>10052493754</t>
+          <t>10065055052</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Panevezys 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>155.00</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MOIR Iona (TIN)</t>
+          <t>BLASZCZAK Joanna</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>10064562978</t>
+          <t>10052493754</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>29 Jan 2023</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11792,49 +11792,49 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>141.00</t>
+          <t>147.00</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MOIR Iona (TIN)</t>
+          <t>BLASZCZAK Joanna</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>10064562978</t>
+          <t>10052493754</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -11844,49 +11844,49 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>141.00</t>
+          <t>147.00</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WEZYK Natalia</t>
+          <t>MOIR Iona (TIN)</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>10053904294</t>
+          <t>10064562978</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>18 Sep 2022</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11896,49 +11896,49 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
+          <t>British Cycling National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>141.00</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WEZYK Natalia</t>
+          <t>MOIR Iona (TIN)</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>10053904294</t>
+          <t>10064562978</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11948,49 +11948,49 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>141.00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LAWRENCE Stephanie (STR)</t>
+          <t>WEZYK Natalia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>10064643006</t>
+          <t>10053904294</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>18 Sep 2022</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12000,91 +12000,91 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Women Elite - Time Trial - General Classification</t>
+          <t>Polish National Championships Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>135.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LAWRENCE Stephanie (STR)</t>
+          <t>WEZYK Natalia</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>10064643006</t>
+          <t>10053904294</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>135.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CHRISTIAN Sylese</t>
+          <t>LAWRENCE Stephanie (STR)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>10045947163</t>
+          <t>10064643006</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12094,173 +12094,173 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>132.00</t>
+          <t>135.00</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EDMUNDS Rhian (TIN)</t>
+          <t>LAWRENCE Stephanie (STR)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>10096737777</t>
+          <t>10064643006</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>130.00</t>
+          <t>135.00</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SAVARD Emy</t>
+          <t>CHRISTIAN Sylese</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>10056270690</t>
+          <t>10045947163</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>120.00</t>
+          <t>132.00</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SAVARD Emy</t>
+          <t>EDMUNDS Rhian (TIN)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>10056270690</t>
+          <t>10096737777</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -12270,195 +12270,195 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>120.00</t>
+          <t>130.00</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HERRERA TERAN Danna</t>
+          <t>SAVARD Emy</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>10094277112</t>
+          <t>10056270690</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>108.00</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SATO Mina (RKD)</t>
+          <t>SAVARD Emy</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>10020784353</t>
+          <t>10056270690</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Japan Track National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GROS Mathilde</t>
+          <t>HERRERA TERAN Danna</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>10015528367</t>
+          <t>10094277112</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Championnats de France Elite Piste 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>108.00</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>JITMAT Yaowaret</t>
+          <t>SATO Mina (RKD)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>10072421190</t>
+          <t>10020784353</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>25 Sep 2022</t>
+          <t>12 May 2023</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Thailand Track National Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Japan Track National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -12488,29 +12488,29 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ALMANZA CHORE Kenia Karina</t>
+          <t>GROS Mathilde</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>10010883784</t>
+          <t>10015528367</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>04 Jan 2023</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CAMPEONATO NACIONAL DE PISTA 2023 - Women Elite - Time Trial - General Classification</t>
+          <t>Championnats de France Elite Piste 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -12540,29 +12540,29 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>VAN DEVENTER Odette</t>
+          <t>JITMAT Yaowaret</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>10009159612</t>
+          <t>10072421190</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>01 Apr 2023</t>
+          <t>25 Sep 2022</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SA National Track Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Thailand Track National Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -12592,29 +12592,29 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>MULLER Maria Tereza</t>
+          <t>ALMANZA CHORE Kenia Karina</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>10007268516</t>
+          <t>10010883784</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>08 Mar 2023</t>
+          <t>28 Apr 2023</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Campeonato Brasileiro de Pista Elite S23 - Women Elite - Time Trial - General Classification</t>
+          <t>CAMPEONATO NACIONAL DE PISTA 2023 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HEMMSEN Karoline</t>
+          <t>VAN DEVENTER Odette</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>10016026000</t>
+          <t>10009159612</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>14 Jan 2023</t>
+          <t>01 Apr 2023</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>National Championship - Time Trial/Individual Pursuit - Women Elite - Time Trial - General Classification</t>
+          <t>SA National Track Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -12696,29 +12696,29 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>107</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PAUL Triyasha</t>
+          <t>MULLER Maria Tereza</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>10087566126</t>
+          <t>10007268516</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>14 Dec 2022</t>
+          <t>08 Mar 2023</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>74TH NATIONAL TRACK CYCLING CHAMPIONSHIPS - Women Elite - Time Trial - General Classification</t>
+          <t>Campeonato Brasileiro de Pista Elite S23 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -12748,29 +12748,29 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MOI Sonja</t>
+          <t>HEMMSEN Karoline</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>10081888491</t>
+          <t>10016026000</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>11 Dec 2022</t>
+          <t>14 Jan 2023</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NM Bane - Women Elite - Time Trial - General Classification</t>
+          <t>National Championship - Time Trial/Individual Pursuit - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -12800,29 +12800,29 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CATINEANU Catalina-Andreea</t>
+          <t>PAUL Triyasha</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>10090504317</t>
+          <t>10087566126</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20 Nov 2022</t>
+          <t>14 Dec 2022</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>National Track Championships - Romania - Women Elite - Time Trial - General Classification</t>
+          <t>74TH NATIONAL TRACK CYCLING CHAMPIONSHIPS - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -12852,29 +12852,29 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>KOZIEVA Nafosat (TTT)</t>
+          <t>MOI Sonja</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>10015504523</t>
+          <t>10081888491</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20 Aug 2022</t>
+          <t>11 Dec 2022</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>The National Championship of Uzbekistan - Women Elite - Time Trial - General Classification</t>
+          <t>NM Bane - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>111</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>KOZIEVA Nafosat (TTT)</t>
+          <t>CATINEANU Catalina-Andreea</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>10015504523</t>
+          <t>10090504317</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>20 Nov 2022</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
+          <t>National Track Championships - Romania - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12956,29 +12956,29 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PRINTEZI Christina</t>
+          <t>KOZIEVA Nafosat (TTT)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>10006306091</t>
+          <t>10015504523</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>GRE</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>20 Aug 2022</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Greek Track National Championships 2022 Elite - Women Elite - Time Trial - General Classification</t>
+          <t>The National Championship of Uzbekistan - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -13008,29 +13008,29 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>SAVOLAINEN Sini</t>
+          <t>KOZIEVA Nafosat (TTT)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>10013498239</t>
+          <t>10015504523</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>17 Jul 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -13040,17 +13040,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rata-sm 2022 part1 - Women Elite - Time Trial - General Classification</t>
+          <t>Track Asia Cup 2022 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>KHANKISHIYEVA Ayan</t>
+          <t>PRINTEZI Christina</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>10063913179</t>
+          <t>10006306091</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>GRE</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>24 Jul 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Azebaijan National Championships - Women Under 23 - Time Trial - General Classification</t>
+          <t>Greek Track National Championships 2022 Elite - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -13112,81 +13112,81 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MIKŠANÍKOVÁ Natálie</t>
+          <t>SAVOLAINEN Sini</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>10056227749</t>
+          <t>10013498239</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>12 Feb 2023</t>
+          <t>17 Jul 2022</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Rata-sm 2022 part1 - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>115</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SOLOVYEVA Anzhela</t>
+          <t>KHANKISHIYEVA Ayan</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>10036104087</t>
+          <t>10063913179</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>12 Apr 2023</t>
+          <t>24 Jul 2022</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13196,129 +13196,233 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kazakhstan National Championships - Women Elite - Time Trial - General Classification</t>
+          <t>Azebaijan National Championships - Women Under 23 - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>GENEST Lauriane (NCI)</t>
+          <t>MIKŠANÍKOVÁ Natálie</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>10011157206</t>
+          <t>10056227749</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>12 Feb 2023</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
+          <t>2023 UEC Track Continental Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
+          <t>SOLOVYEVA Anzhela</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>10036104087</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>12 Apr 2023</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>NCh</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Kazakhstan National Championships - Women Elite - Time Trial - General Classification</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>GENEST Lauriane (NCI)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>10011157206</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>08 Jan 2023</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>NCh</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2022 Canadian Track Championships (Elite/Masters) - Women Elite - Time Trial - General Classification</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
           <t>SAKAI Aki</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>10021474972</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>JPN</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>12 May 2023</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>NCh</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="F250" t="inlineStr">
         <is>
           <t>Japan Track National Championships - Women Elite - Time Trial - General Classification</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G250" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H250" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I250" t="inlineStr">
         <is>
           <t>90.00</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr">
+      <c r="J250" t="inlineStr">
         <is>
           <t>120</t>
         </is>

--- a/pages/Time_Trial_Points_Women.xlsx
+++ b/pages/Time_Trial_Points_Women.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>02 Jan 2023</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>02 Jan 2023</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>23 Dec 2022</t>
+          <t>02 Jan 2023</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>30 Apr 2023</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>01 Apr 2023</t>
+          <t>05 Apr 2023</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>08 Mar 2023</t>
+          <t>12 Mar 2023</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
